--- a/Result/profitability/1558.xlsx
+++ b/Result/profitability/1558.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.85</v>
       </c>
       <c r="M2" t="n">
-        <v>1.365</v>
+        <v>1.51125</v>
       </c>
       <c r="N2" t="n">
-        <v>26.37875</v>
+        <v>26.035</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.5</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1725</v>
+        <v>1.4125</v>
       </c>
       <c r="N3" t="n">
-        <v>25.06625</v>
+        <v>24.445</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.63</v>
       </c>
       <c r="M4" t="n">
-        <v>1.09</v>
+        <v>1.335</v>
       </c>
       <c r="N4" t="n">
-        <v>23.25625</v>
+        <v>23.375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>1.41</v>
       </c>
       <c r="M5" t="n">
-        <v>1.11</v>
+        <v>1.415</v>
       </c>
       <c r="N5" t="n">
-        <v>22.41125</v>
+        <v>22.3325</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>1.37</v>
       </c>
       <c r="M6" t="n">
-        <v>1.185</v>
+        <v>1.305</v>
       </c>
       <c r="N6" t="n">
-        <v>22.36375</v>
+        <v>22.22125</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>2.4</v>
       </c>
       <c r="M7" t="n">
-        <v>1.20375</v>
+        <v>1.45</v>
       </c>
       <c r="N7" t="n">
-        <v>22.59625</v>
+        <v>22.33375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1276,7 +1276,7 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
@@ -1285,7 +1285,7 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>3.53</v>
       </c>
       <c r="M8" t="n">
-        <v>1.49</v>
+        <v>1.7375</v>
       </c>
       <c r="N8" t="n">
-        <v>22.925</v>
+        <v>23.1825</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1558</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2292</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1690</v>
+      </c>
+      <c r="E75" t="n">
+        <v>602</v>
+      </c>
+      <c r="F75" t="n">
+        <v>26.26</v>
+      </c>
+      <c r="G75" t="n">
+        <v>232</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>10.13%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>140</v>
+      </c>
+      <c r="J75" t="n">
+        <v>372</v>
+      </c>
+      <c r="K75" t="n">
+        <v>207</v>
+      </c>
+      <c r="L75" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="N75" t="n">
+        <v>27.3325</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.609756097560976</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.060000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.08512396694214885</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>3.168831168831169</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.629999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.02342878393454817</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
